--- a/umkm_summary.xlsx
+++ b/umkm_summary.xlsx
@@ -439,7 +439,7 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
@@ -589,47 +589,47 @@
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>68.8</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pantau</t>
+          <t>Baik</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N2" t="n">
         <v>100</v>
       </c>
       <c r="O2" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pengiriman</t>
+          <t>Tidak ada</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Rekomendasi mitra ekspedisi yang lebih handal</t>
+          <t>Pertahankan kualitas produk dan layanan saat ini</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Pelatihan manajemen pengiriman</t>
+          <t>Berpotensi dijadikan UMKM percontohan binaan Diskop</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -638,11 +638,7 @@
           <t>Batik Banyumas yang berkualitas. Ada harga, ada kualitas, Batik tulisnya keren keren, Harganya terjangkau, batiknya bagus dan keren</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Buat yang nyari batik Banyumas yg original (asli lukisan dan pewarnaan orang Banyumas)  tempat ini salah satu yg recomended. Sering bawa tamu dr dalam dan luar negeri</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -674,16 +670,16 @@
         <v>11</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>63.6</v>
+        <v>54.5</v>
       </c>
       <c r="J3" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -691,7 +687,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="M3" t="n">
         <v>50</v>
@@ -841,19 +837,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -861,38 +857,38 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O5" t="n">
         <v>50</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kualitas</t>
+          <t>Harga</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Kunjungan lapangan untuk evaluasi proses produksi</t>
+          <t>Analisis struktur biaya dengan konsultan Diskop</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Pendampingan quality control</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Analisis struktur biaya dengan konsultan Diskop</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>Evaluasi strategi penetapan harga</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Istimewa , rasanya mantap .</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>Soto nya manis, spt nya tidak menggunakan vetsin atau penyedap rasa dan lbh mengandalkan gula sbg penyedap dan kuah kurang panas. Ketika mencoba tambah garam malah rasanya jadi aneh.  Utk penikmat soto dgn rasa yg gurih, agak kurang cocok.</t>
@@ -926,33 +922,33 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="J6" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Kritis</t>
+          <t>Perlu Perhatian</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M6" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="N6" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1018,20 +1014,20 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="J7" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Pantau</t>
+          <t>Baik</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1041,24 +1037,24 @@
         <v>50</v>
       </c>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O7" t="n">
         <v>50</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Harga</t>
+          <t>Tidak ada</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Analisis struktur biaya dengan konsultan Diskop</t>
+          <t>Pertahankan kualitas produk dan layanan saat ini</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Evaluasi strategi penetapan harga</t>
+          <t>Berpotensi dijadikan UMKM percontohan binaan Diskop</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1120,10 +1116,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N8" t="n">
         <v>60</v>
@@ -1133,17 +1129,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Packaging</t>
+          <t>Kualitas</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Ikutkan dalam pelatihan packaging Diskop</t>
+          <t>Kunjungan lapangan untuk evaluasi proses produksi</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Konsultasi desain kemasan dengan mentor</t>
+          <t>Pendampingan quality control</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1153,7 +1149,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Okelah.. singkongnya ok banget... Kopi Wamena nya jossssnya pooolll... tempe Mendoaannya garing garing...</t>
+          <t>Tempatnya nyaman dengan suasananya ala vintage, harga makanan dan minumannya worth it untuk kantong mahasiswa dan pekerja.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1192,16 +1188,16 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="J9" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1209,30 +1205,30 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="O9" t="n">
         <v>100</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Harga</t>
+          <t>Tidak ada</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Analisis struktur biaya dengan konsultan Diskop</t>
+          <t>Pertahankan kualitas produk dan layanan saat ini</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Evaluasi strategi penetapan harga</t>
+          <t>Berpotensi dijadikan UMKM percontohan binaan Diskop</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1241,11 +1237,7 @@
           <t>Keren dan berkualitas</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Batiknya banyak pilihan. Pemesanan bisa juga melalui WA untuk mengecek ketersediaannya. Pembayaran juga dapat dilakukan secara non tunai.</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1258,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1543,7 +1535,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -1679,7 +1671,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -2019,7 +2011,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2359,7 +2351,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -2427,7 +2419,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2971,7 +2963,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -3997,7 +3989,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -4065,7 +4057,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -4395,12 +4387,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Rasa tidak seenak dulu dan harga saya rasa terlalu mahal buat soto dgn porsi kecil yg spt itu. Juga tidak adanya lahan parkir yg membuat susah bila mau mengunjungi warung ini</t>
+          <t>Makanan biasa aja.harga termasuk mahal klo di kampung</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>tidak enak harga mahal soto porsi spt tidak lahan parkir susah unjung warung</t>
+          <t>makan harga mahal klo kampung</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4409,13 +4401,13 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.003</v>
+        <v>0.0234</v>
       </c>
       <c r="L46" t="n">
-        <v>0.997</v>
+        <v>0.9766</v>
       </c>
       <c r="M46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -4462,166 +4454,166 @@
         <v>9</v>
       </c>
       <c r="H47" t="inlineStr">
-        <is>
-          <t>Makanan biasa aja.harga termasuk mahal klo di kampung</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>makan harga mahal klo kampung</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>0.0234</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.9766</v>
-      </c>
-      <c r="M47" t="b">
-        <v>0</v>
-      </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
-      <c r="O47" t="b">
-        <v>1</v>
-      </c>
-      <c r="P47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>R004</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Soto Sangka Banyumas</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Kuliner</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Banyumas</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Soto, makanan khas Purwokerto, dan minuman</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Google Maps (manual)</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>10</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Harga relatif mahal dengan rasa yang biasa saja (ga spesial)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>harga relatif mahal ga spesial</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>0.0524</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0.9476</v>
-      </c>
-      <c r="M48" t="b">
-        <v>1</v>
-      </c>
-      <c r="N48" t="b">
-        <v>0</v>
-      </c>
-      <c r="O48" t="b">
-        <v>1</v>
-      </c>
-      <c r="P48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>R004</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Soto Sangka Banyumas</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Kuliner</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Banyumas</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Soto, makanan khas Purwokerto, dan minuman</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Google Maps (manual)</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>11</v>
-      </c>
-      <c r="H49" t="inlineStr">
         <is>
           <t>Soto nya manis, spt nya tidak menggunakan vetsin atau penyedap rasa dan lbh mengandalkan gula sbg penyedap dan kuah kurang panas.
 Ketika mencoba tambah garam malah rasanya jadi aneh.
 Utk penikmat soto dgn rasa yg gurih, agak kurang cocok.</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>soto manis spt tidak vetsin sedap lbh andal gula sbg sedap kuah kurang panas coba garam aneh nikmat soto gurih kurang cocok</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="M47" t="b">
+        <v>1</v>
+      </c>
+      <c r="N47" t="b">
+        <v>0</v>
+      </c>
+      <c r="O47" t="b">
+        <v>0</v>
+      </c>
+      <c r="P47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Soto Sangka Banyumas</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Kuliner</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Banyumas</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Soto, makanan khas Purwokerto, dan minuman</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Google Maps (manual)</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>10</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kalo tanpa sambal kacangnya tawar menurut saya, harga semangkok kecil dengan 4 potong kupat Rp 16.000, menurut saya mahal. Cukup sekali.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>kalo tanpa sambal kacang tawar harga semangkok potong kupat rp mahal</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.8963</v>
+      </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O48" t="b">
+        <v>1</v>
+      </c>
+      <c r="P48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>R004</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Soto Sangka Banyumas</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Kuliner</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Banyumas</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Soto, makanan khas Purwokerto, dan minuman</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Google Maps (manual)</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>11</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Soto ayam yang nikmat, dengan suasana jadul yang legendaris.. Membuat kita seperti kembali ke tempo dulu.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>soto manis spt tidak vetsin sedap lbh andal gula sbg sedap kuah kurang panas coba garam aneh nikmat soto gurih kurang cocok</t>
+          <t>soto ayam nikmat suasana jadul legendaris tempo</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.0025</v>
+        <v>0.4722</v>
       </c>
       <c r="L49" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.5278</v>
       </c>
       <c r="M49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -4669,27 +4661,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kalo tanpa sambal kacangnya tawar menurut saya, harga semangkok kecil dengan 4 potong kupat Rp 16.000, menurut saya mahal. Cukup sekali.</t>
+          <t>Enak lhoo yaa.. soto banyumas… mangkoknya kecil macam mangkuk dawet kalo di jogja. Trusnya kuahnya kuning.. kacangnya utuh. Sambalnya sambal kacang… jadi kalo tidak biasa makan sroto.. cobain soto disini… soto disini tidak seperti sroto2 di purwokerto atau tempat lain.. Utk harga jangan kaget c.. Buat warga jagja solo boyolali semarang.. yang biasa makan soto semangkuk 10ribu bahkan kurang… soto di banyumas yang legend rata harga 20rb keatas.. hahaha..</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>kalo tanpa sambal kacang tawar harga semangkok potong kupat rp mahal</t>
+          <t>enak lhoo yaa soto banyumas mangkok mangkuk dawet kalo jogja trusnya kuah kuning kacang utuh sambal sambal kacang kalo tidak makan sroto cobain soto soto tidak sroto purwokerto harga jangan kaget warga jagja solo boyolali semarang makan soto semangkuk ribu kurang soto banyumas legend harga rb atas hahaha</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>0.1037</v>
+        <v>0.0017</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8963</v>
+        <v>0.9983</v>
       </c>
       <c r="M50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
@@ -4737,27 +4729,27 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Soto ayam yang nikmat, dengan suasana jadul yang legendaris.. Membuat kita seperti kembali ke tempo dulu.</t>
+          <t>Rasa sotonya enak, walaupun bukan yang paling enak, yang dirasakan saat makan disini adalah nostalgia nya, dulu pernah makan disini saat masih SD, masaknya pun masih menggunakan tungku kayu bakar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>soto ayam nikmat suasana jadul legendaris tempo</t>
+          <t>soto enak bukan enak rasa makan nostalgia makan sd masak tungku kayu bakar</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>0.4722</v>
+        <v>0.3568</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5278</v>
+        <v>0.6432</v>
       </c>
       <c r="M51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -4772,12 +4764,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kopi Kami, Untuk Kamu</t>
+          <t>Soto Sangka Banyumas</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4787,12 +4779,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Purwokerto Utara</t>
+          <t>Banyumas</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kopi, minuman espresso based, makanan ringan, dan menu kafe</t>
+          <t>Soto, makanan khas Purwokerto, dan minuman</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4801,31 +4793,31 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Lokasinya strategis, tempatnya nyaman full AC ada 2 lantai, klo makan di kemangi bisa pesan menu di kopi kami karena 1 managemen.</t>
+          <t>Selalu kesini kalau ke banyumas, soto nya enakkk.. rasa tidak pernah berubah dari jaman masih SD</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>lokasi strategis tempat nyaman full ac lantai klo makan kemangi pesan menu kopi managemen</t>
+          <t>kesini banyumas soto enakkk tidak ubah jaman sd</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>0.1143</v>
+        <v>0.074</v>
       </c>
       <c r="L52" t="n">
-        <v>0.8857</v>
+        <v>0.926</v>
       </c>
       <c r="M52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" t="b">
         <v>1</v>
@@ -4840,12 +4832,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R005</t>
+          <t>R004</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kopi Kami, Untuk Kamu</t>
+          <t>Soto Sangka Banyumas</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4855,12 +4847,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Purwokerto Utara</t>
+          <t>Banyumas</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kopi, minuman espresso based, makanan ringan, dan menu kafe</t>
+          <t>Soto, makanan khas Purwokerto, dan minuman</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4869,16 +4861,16 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman, adem, banyak kursi, ada mushola, harga affordable, free wifi. The best pokoknya. Semoga rame yaa...</t>
+          <t>Istimewa , rasanya mantap .</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>tempat nyaman adem kursi mushola harga affordable free wifi the best pokok moga rame yaa</t>
+          <t>istimewa mantap</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4887,19 +4879,19 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0.9994</v>
+        <v>0.9999</v>
       </c>
       <c r="L53" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0001</v>
       </c>
       <c r="M53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="b">
         <v>0</v>
@@ -4937,16 +4929,16 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tempatnya cozy banget buat makan &amp; nongkrong mantep, tatanan interiornya suka sih keren, untuk makanannya lumayan enak</t>
+          <t>Lokasinya strategis, tempatnya nyaman full AC ada 2 lantai, klo makan di kemangi bisa pesan menu di kopi kami karena 1 managemen.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>tempat cozy makan nongkrong mantep tatanan interior suka keren makan lumayan enak</t>
+          <t>lokasi strategis tempat nyaman full ac lantai klo makan kemangi pesan menu kopi managemen</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4955,16 +4947,16 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>0.9971</v>
+        <v>0.1143</v>
       </c>
       <c r="L54" t="n">
-        <v>0.0029</v>
+        <v>0.8857</v>
       </c>
       <c r="M54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="b">
         <v>0</v>
@@ -5005,37 +4997,37 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pelayanan kurang memuaskan....rasa mkanan biasa aja</t>
+          <t>Tempatnya nyaman, adem, banyak kursi, ada mushola, harga affordable, free wifi. The best pokoknya. Semoga rame yaa...</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>layan kurang muas mkanan</t>
+          <t>tempat nyaman adem kursi mushola harga affordable free wifi the best pokok moga rame yaa</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0.0172</v>
+        <v>0.9994</v>
       </c>
       <c r="L55" t="n">
-        <v>0.9828</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="M55" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" t="b">
         <v>0</v>
@@ -5073,40 +5065,40 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>pernah aku dan keluarga makan disini dan sampe 1 jam lebih nunggu makanan dateng, yang tadi'nya laper mau makan biar kenyang karena nunggu kelamaan lapernya ilang, sampe makanan blm dteng semua kita pulang, dan kita memutuskan makanan yg dipesan untuk di bungkus, dan lebih parahnya lgi makanan yg udah masuk bill 1 macem makanan ternyata tdk ada pas smpe rumah, sekedar masukan harap lebih menghargai pelanggan, terimakasih.</t>
+          <t>Tempatnya cozy banget buat makan &amp; nongkrong mantep, tatanan interiornya suka sih keren, untuk makanannya lumayan enak</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>keluarga makan sampe jam nunggu makan dateng laper makan biar kenyang nunggu lapernya ilang sampe makan blm dteng pulang putus makan pes bungkus parah lgi makan masuk bill macem makan tdk pas smpe rumah dar masuk harap harga langgan</t>
+          <t>tempat cozy makan nongkrong mantep tatanan interior suka keren makan lumayan enak</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0.0104</v>
+        <v>0.9971</v>
       </c>
       <c r="L56" t="n">
-        <v>0.9896</v>
+        <v>0.0029</v>
       </c>
       <c r="M56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5141,16 +5133,16 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Layanannya lama..butuh 15 menit sampai ada 1 pelayan yg tanyain mau pesen apa dan butuh 15 menit lagi untuk menunggu 1 gelas 1 latte..panas dan rame banget..wifi ada tapi gak ada connection..sayang bgt padahal tempatnya bagus dan harganya affordable.</t>
+          <t>Pelayanan kurang memuaskan....rasa mkanan biasa aja</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>layan butuh menit layan tanyain sen butuh menit tunggu gelas latte panas rame wifi gak connection sayang tempat bagus harga affordable</t>
+          <t>layan kurang muas mkanan</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -5159,10 +5151,10 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0.433</v>
+        <v>0.0172</v>
       </c>
       <c r="L57" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.9828</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
@@ -5171,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="O57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5209,16 +5201,16 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Mohon maaf saya berikan bintang 1. Pernah makan di sini dan pesanan datang lama sekali hampir 1 jam padahal di sana tidak banyak tamu. Mohon diperbaiki pelayanan nya, Tempat yang nyaman akan sia-sia jika masakan disajikan terlalu lama.</t>
+          <t>pernah aku dan keluarga makan disini dan sampe 1 jam lebih nunggu makanan dateng, yang tadi'nya laper mau makan biar kenyang karena nunggu kelamaan lapernya ilang, sampe makanan blm dteng semua kita pulang, dan kita memutuskan makanan yg dipesan untuk di bungkus, dan lebih parahnya lgi makanan yg udah masuk bill 1 macem makanan ternyata tdk ada pas smpe rumah, sekedar masukan harap lebih menghargai pelanggan, terimakasih.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>mohon maaf bintang makan pesan jam tidak tamu mohon baik layan nyaman sia sia masakan saji</t>
+          <t>keluarga makan sampe jam nunggu makan dateng laper makan biar kenyang nunggu lapernya ilang sampe makan blm dteng pulang putus makan pes bungkus parah lgi makan masuk bill macem makan tdk pas smpe rumah dar masuk harap harga langgan</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5227,10 +5219,10 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.0072</v>
+        <v>0.0104</v>
       </c>
       <c r="L58" t="n">
-        <v>0.9928</v>
+        <v>0.9896</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -5239,7 +5231,7 @@
         <v>1</v>
       </c>
       <c r="O58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
@@ -5277,16 +5269,16 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Harga tinggi, rasa rendah</t>
+          <t>Layanannya lama..butuh 15 menit sampai ada 1 pelayan yg tanyain mau pesen apa dan butuh 15 menit lagi untuk menunggu 1 gelas 1 latte..panas dan rame banget..wifi ada tapi gak ada connection..sayang bgt padahal tempatnya bagus dan harganya affordable.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>harga rendah</t>
+          <t>layan butuh menit layan tanyain sen butuh menit tunggu gelas latte panas rame wifi gak connection sayang tempat bagus harga affordable</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5295,10 +5287,10 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>0.2259</v>
+        <v>0.433</v>
       </c>
       <c r="L59" t="n">
-        <v>0.7741</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="M59" t="b">
         <v>1</v>
@@ -5310,7 +5302,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -5345,16 +5337,16 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Pelayanan kurang memuaskan....rasa mkanan biasa aja</t>
+          <t>Mohon maaf saya berikan bintang 1. Pernah makan di sini dan pesanan datang lama sekali hampir 1 jam padahal di sana tidak banyak tamu. Mohon diperbaiki pelayanan nya, Tempat yang nyaman akan sia-sia jika masakan disajikan terlalu lama.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>layan kurang muas mkanan</t>
+          <t>mohon maaf bintang makan pesan jam tidak tamu mohon baik layan nyaman sia sia masakan saji</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5363,22 +5355,22 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0.0172</v>
+        <v>0.0072</v>
       </c>
       <c r="L60" t="n">
-        <v>0.9828</v>
+        <v>0.9928</v>
       </c>
       <c r="M60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="b">
         <v>0</v>
       </c>
       <c r="P60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -5413,16 +5405,16 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Pelayanan perlu ditingkatkan lg.</t>
+          <t>Harga tinggi, rasa rendah</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>layan tingkat lg</t>
+          <t>harga rendah</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5431,19 +5423,19 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>0.068</v>
+        <v>0.2259</v>
       </c>
       <c r="L61" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.7741</v>
       </c>
       <c r="M61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
       </c>
       <c r="O61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P61" t="b">
         <v>0</v>
@@ -5481,37 +5473,37 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murah, enak, tempat duduk nyaman, ac. Di sini paling cocok. </t>
+          <t>Pelayanan perlu ditingkatkan lg.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>murah enak duduk nyaman ac cocok</t>
+          <t>layan tingkat lg</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>0.9979</v>
+        <v>0.068</v>
       </c>
       <c r="L62" t="n">
-        <v>0.0021</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="M62" t="b">
         <v>0</v>
       </c>
       <c r="N62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P62" t="b">
         <v>0</v>
@@ -5549,28 +5541,28 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Enak dan tdk mahal juga tempat nyaman</t>
+          <t xml:space="preserve">Murah, enak, tempat duduk nyaman, ac. Di sini paling cocok. </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>enak tdk mahal nyaman</t>
+          <t>murah enak duduk nyaman ac cocok</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>0.4114</v>
+        <v>0.9979</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5886</v>
+        <v>0.0021</v>
       </c>
       <c r="M63" t="b">
         <v>0</v>
@@ -5617,16 +5609,16 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Makanannya ga ada yang fail. Enak2 semua. Minumnya oke, tempatnya enak banget buat kerja yang butuh fokus ekstra</t>
+          <t>Enak dan tdk mahal juga tempat nyaman</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>makan ga fail enak minum oke tempat enak kerja butuh fokus ekstra</t>
+          <t>enak tdk mahal nyaman</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5635,19 +5627,19 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0.5608</v>
+        <v>0.4114</v>
       </c>
       <c r="L64" t="n">
-        <v>0.4392</v>
+        <v>0.5886</v>
       </c>
       <c r="M64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" t="b">
         <v>0</v>
@@ -5656,12 +5648,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R006</t>
+          <t>R005</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nakopi Roastery</t>
+          <t>Kopi Kami, Untuk Kamu</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5671,12 +5663,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Purwokerto Selatan</t>
+          <t>Purwokerto Utara</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Biji Kopi dan minuman kopi pilihan</t>
+          <t>Kopi, minuman espresso based, makanan ringan, dan menu kafe</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5685,31 +5677,31 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Pertama kali kesini, langsung dijelaskan macam macam kopi. Lengkap untuk kopi nya, mau lokal maupun kopi Nusantara. Beli beans gratis giling.</t>
+          <t>Makanannya ga ada yang fail. Enak2 semua. Minumnya oke, tempatnya enak banget buat kerja yang butuh fokus ekstra</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>kali kesini langsung kopi lengkap kopi lokal kopi nusantara beli beans gratis giling</t>
+          <t>makan ga fail enak minum oke tempat enak kerja butuh fokus ekstra</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0.2179</v>
+        <v>0.5608</v>
       </c>
       <c r="L65" t="n">
-        <v>0.7821</v>
+        <v>0.4392</v>
       </c>
       <c r="M65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -5753,16 +5745,16 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Pilihan biji kopi nya beragam dan harga sangat terjangkau, pemilik juga ramah</t>
+          <t>Pertama kali kesini, langsung dijelaskan macam macam kopi. Lengkap untuk kopi nya, mau lokal maupun kopi Nusantara. Beli beans gratis giling.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>pilih biji kopi agam harga jangkau milik ramah</t>
+          <t>kali kesini langsung kopi lengkap kopi lokal kopi nusantara beli beans gratis giling</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5771,10 +5763,10 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.2179</v>
       </c>
       <c r="L66" t="n">
-        <v>0.0217</v>
+        <v>0.7821</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -5783,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="O66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="b">
         <v>0</v>
@@ -5821,16 +5813,16 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tempat jual berbagai macam jenis kopi yang lumayan lengkap. Beans nya bisa minta digiling sekalian. Penjualnya ramah. Kopi nya juga enak dan fresh.</t>
+          <t>Pilihan biji kopi nya beragam dan harga sangat terjangkau, pemilik juga ramah</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>jual jenis kopi lumayan lengkap beans giling jual ramah kopi enak fresh</t>
+          <t>pilih biji kopi agam harga jangkau milik ramah</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5839,19 +5831,19 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0.8756</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>0.1244</v>
+        <v>0.0217</v>
       </c>
       <c r="M67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
       </c>
       <c r="O67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67" t="b">
         <v>0</v>
@@ -5889,37 +5881,37 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tempat jual kopi terdekat dan termurah dari rumah, sudah coba berbagai macam beans, tp blm pernah ketemu sama yang punya…</t>
+          <t>Tempat jual berbagai macam jenis kopi yang lumayan lengkap. Beans nya bisa minta digiling sekalian. Penjualnya ramah. Kopi nya juga enak dan fresh.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>jual kopi dekat murah rumah coba beans blm ketemu</t>
+          <t>jual jenis kopi lumayan lengkap beans giling jual ramah kopi enak fresh</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>0.1114</v>
+        <v>0.8756</v>
       </c>
       <c r="L68" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.1244</v>
       </c>
       <c r="M68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
       </c>
       <c r="O68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" t="b">
         <v>0</v>
@@ -5957,28 +5949,28 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Saya minta giling halus malah dikasih kasar</t>
+          <t>Tempat jual kopi terdekat dan termurah dari rumah, sudah coba berbagai macam beans, tp blm pernah ketemu sama yang punya…</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>giling halus kasih kasar</t>
+          <t>jual kopi dekat murah rumah coba beans blm ketemu</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0.0895</v>
+        <v>0.1114</v>
       </c>
       <c r="L69" t="n">
-        <v>0.9105</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -5987,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="O69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P69" t="b">
         <v>0</v>
@@ -6025,31 +6017,31 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Pilihan beragam, sebagai pecinta arabika, banyak opsi kopi enak dan mantap</t>
+          <t>Saya minta giling halus malah dikasih kasar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>pilih agam cinta arabika opsi kopi enak mantap</t>
+          <t>giling halus kasih kasar</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>0.9918</v>
+        <v>0.0895</v>
       </c>
       <c r="L70" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.9105</v>
       </c>
       <c r="M70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -6093,16 +6085,16 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Ownernya ramah banget, baru kesampean main ke kesini, menyediakan banyak variant kopi. Pembelian kali ini saya ambil robusta temanggung, robusta slamet, dan arabika ratamba. Sudah saya cicip enak semua, fresh gaes. Rekomendasi buat kalian yang suka nyeduh kopi dirumah bareng keluarga, dikantor, maupun sebagai gift ke seseorang.</t>
+          <t>Pilihan beragam, sebagai pecinta arabika, banyak opsi kopi enak dan mantap</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ownernya ramah sampean main kesini sedia variant kopi beli kali ambil robusta tanggung robusta slamet arabika ratamba cicip enak fresh gaes rekomendasi suka nyeduh kopi rumah bareng keluarga kantor gift</t>
+          <t>pilih agam cinta arabika opsi kopi enak mantap</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6111,13 +6103,13 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>0.7991</v>
+        <v>0.9918</v>
       </c>
       <c r="L71" t="n">
-        <v>0.2009</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="M71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
@@ -6161,16 +6153,16 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Mantaaapp..pilihan kopi banyak..karyawan toko (mas Nazal) ramah,sumeh seperti ownernya..</t>
+          <t>Ownernya ramah banget, baru kesampean main ke kesini, menyediakan banyak variant kopi. Pembelian kali ini saya ambil robusta temanggung, robusta slamet, dan arabika ratamba. Sudah saya cicip enak semua, fresh gaes. Rekomendasi buat kalian yang suka nyeduh kopi dirumah bareng keluarga, dikantor, maupun sebagai gift ke seseorang.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>mantaaapp pilih kopi karyawan toko mas nazal ramah sumeh ownernya</t>
+          <t>ownernya ramah sampean main kesini sedia variant kopi beli kali ambil robusta tanggung robusta slamet arabika ratamba cicip enak fresh gaes rekomendasi suka nyeduh kopi rumah bareng keluarga kantor gift</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6179,10 +6171,10 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>0.6968</v>
+        <v>0.7991</v>
       </c>
       <c r="L72" t="n">
-        <v>0.3032</v>
+        <v>0.2009</v>
       </c>
       <c r="M72" t="b">
         <v>0</v>
@@ -6229,16 +6221,16 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tempat beli kopi mantap, enak, spesial pokoknya recomended beli kpi disini</t>
+          <t>Mantaaapp..pilihan kopi banyak..karyawan toko (mas Nazal) ramah,sumeh seperti ownernya..</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>beli kopi mantap enak spesial pokok recomended beli kpi</t>
+          <t>mantaaapp pilih kopi karyawan toko mas nazal ramah sumeh ownernya</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6247,13 +6239,13 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>0.9847</v>
+        <v>0.6968</v>
       </c>
       <c r="L73" t="n">
-        <v>0.0153</v>
+        <v>0.3032</v>
       </c>
       <c r="M73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
@@ -6297,16 +6289,16 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kualitas kopi nya top dan pelayanan nya ramah poll</t>
+          <t>Tempat beli kopi mantap, enak, spesial pokoknya recomended beli kpi disini</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>kualitas kopi top layan ramah poll</t>
+          <t>beli kopi mantap enak spesial pokok recomended beli kpi</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6315,10 +6307,10 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>0.9759</v>
+        <v>0.9847</v>
       </c>
       <c r="L74" t="n">
-        <v>0.0241</v>
+        <v>0.0153</v>
       </c>
       <c r="M74" t="b">
         <v>1</v>
@@ -6336,12 +6328,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>R007</t>
+          <t>R006</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Praketa</t>
+          <t>Nakopi Roastery</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6351,12 +6343,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Purwokerto Utara</t>
+          <t>Purwokerto Selatan</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kopi, minuman espresso based, makanan ringan, dan menu kafe</t>
+          <t>Biji Kopi dan minuman kopi pilihan</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6365,16 +6357,16 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>My personal experience here has always been good. Praketa nyaman banget untuk nugas. Ada colokan di setiap meja. Kalau kurang, bisa minta roll kabel tambahan. Pesan apapun juga free segelas air mineral. No bayar parkir, karena mereka juga menyediakan kartu parkir gratis. Daaaan, wifinya kenceng banget. Online meeting disini lancar jaya. Makanannya juga affordable. Paling suka ricebowl crispy chicken yang sambel matah atau ricebowl bakso sapi saus bbq. Intinya Praketa is my personal comfort place. The service is too good. I think I come here at least twice a month, except during holiday??</t>
+          <t>Kualitas kopi nya top dan pelayanan nya ramah poll</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>my personal experience here has always been good praketa nyaman nugas colok meja kurang roll kabel tambah pesan apa free gelas air mineral no bayar parkir sedia kartu parkir gratis daaaan wifinya kenceng online meeting lancar jaya makan affordable suka ricebowl crispy chicken sambel matah ricebowl bakso sapi saus bbq inti praketa is my personal comfort place the service is too good think come here at least twice month except during holiday</t>
+          <t>kualitas kopi top layan ramah poll</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6383,19 +6375,19 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0.8784</v>
+        <v>0.9759</v>
       </c>
       <c r="L75" t="n">
-        <v>0.1216</v>
+        <v>0.0241</v>
       </c>
       <c r="M75" t="b">
         <v>1</v>
       </c>
       <c r="N75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P75" t="b">
         <v>0</v>
@@ -6433,37 +6425,37 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Another cafe deket Unsoed yang aku rekomendasiin juga. Tempatnya kecil tapi nyaman kok, ada ruang indoor dan outdoornya. Parkiran luas, ada buku juga yang bisa dibaca sambil minum kopi</t>
+          <t>My personal experience here has always been good. Praketa nyaman banget untuk nugas. Ada colokan di setiap meja. Kalau kurang, bisa minta roll kabel tambahan. Pesan apapun juga free segelas air mineral. No bayar parkir, karena mereka juga menyediakan kartu parkir gratis. Daaaan, wifinya kenceng banget. Online meeting disini lancar jaya. Makanannya juga affordable. Paling suka ricebowl crispy chicken yang sambel matah atau ricebowl bakso sapi saus bbq. Intinya Praketa is my personal comfort place. The service is too good. I think I come here at least twice a month, except during holiday??</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>another cafe deket unsoed rekomendasiin tempat nyaman ruang indoor outdoornya parkir luas buku baca minum kopi</t>
+          <t>my personal experience here has always been good praketa nyaman nugas colok meja kurang roll kabel tambah pesan apa free gelas air mineral no bayar parkir sedia kartu parkir gratis daaaan wifinya kenceng online meeting lancar jaya makan affordable suka ricebowl crispy chicken sambel matah ricebowl bakso sapi saus bbq inti praketa is my personal comfort place the service is too good think come here at least twice month except during holiday</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>0.2186</v>
+        <v>0.8784</v>
       </c>
       <c r="L76" t="n">
-        <v>0.7814</v>
+        <v>0.1216</v>
       </c>
       <c r="M76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="b">
         <v>1</v>
       </c>
       <c r="O76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76" t="b">
         <v>0</v>
@@ -6501,40 +6493,40 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>mahall, pesanannya lama, kurang hemat untuk kaum mendang mending.</t>
+          <t>Another cafe deket Unsoed yang aku rekomendasiin juga. Tempatnya kecil tapi nyaman kok, ada ruang indoor dan outdoornya. Parkiran luas, ada buku juga yang bisa dibaca sambil minum kopi</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>mahall pesan kurang hemat kaum dang mending</t>
+          <t>another cafe deket unsoed rekomendasiin tempat nyaman ruang indoor outdoornya parkir luas buku baca minum kopi</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0.0011</v>
+        <v>0.2186</v>
       </c>
       <c r="L77" t="n">
-        <v>0.9989</v>
+        <v>0.7814</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6569,16 +6561,16 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Total 74rb praketa skrg downgrade bgt, Kentang berapa biji 15ribu, risol mayo 3biji 18rb, lemon tea cup ketcil 18rb, caffe latte 23rb, total 74ribu ini becanda apa gmn kaya nggelitik lidah doang. Mending ke coffe shop lain, bye praketa…</t>
+          <t>mahall, pesanannya lama, kurang hemat untuk kaum mendang mending.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>total rb praketa skrg downgrade kentang biji ribu risol mayo biji rb lemon tea cup ketcil rb caffe latte rb total ribu becanda gmn kaya nggelitik lidah doang mending coffe shop bye praketa</t>
+          <t>mahall pesan kurang hemat kaum dang mending</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6587,10 +6579,10 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>0.0173</v>
+        <v>0.0011</v>
       </c>
       <c r="L78" t="n">
-        <v>0.9827</v>
+        <v>0.9989</v>
       </c>
       <c r="M78" t="b">
         <v>0</v>
@@ -6599,10 +6591,10 @@
         <v>0</v>
       </c>
       <c r="O78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -6637,16 +6629,16 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Pelayanannya kurang ramah, terkesan maksa untuk semua order padahal pasti di order. But i think kan bisa aja sharing. Even emg mau mengingatkan coba pelan² mbaa...</t>
+          <t>Total 74rb praketa skrg downgrade bgt, Kentang berapa biji 15ribu, risol mayo 3biji 18rb, lemon tea cup ketcil 18rb, caffe latte 23rb, total 74ribu ini becanda apa gmn kaya nggelitik lidah doang. Mending ke coffe shop lain, bye praketa…</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>layan kurang ramah kes maksa order order but think sharing even emg coba pelan mbaa</t>
+          <t>total rb praketa skrg downgrade kentang biji ribu risol mayo biji rb lemon tea cup ketcil rb caffe latte rb total ribu becanda gmn kaya nggelitik lidah doang mending coffe shop bye praketa</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6655,10 +6647,10 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>0.1152</v>
+        <v>0.0173</v>
       </c>
       <c r="L79" t="n">
-        <v>0.8848</v>
+        <v>0.9827</v>
       </c>
       <c r="M79" t="b">
         <v>0</v>
@@ -6705,16 +6697,16 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Punten ya min, habis dapet pelayanan yang kurang mengenakan dr mba mba nya, kalau menawarkan bisa jgn terlalu maksa gitu, mengangu kenyaman sebagai customer, apa lg dengan nada bicara yang kurang humbel, terimaksi????</t>
+          <t>Pelayanannya kurang ramah, terkesan maksa untuk semua order padahal pasti di order. But i think kan bisa aja sharing. Even emg mau mengingatkan coba pelan² mbaa...</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>punten min habis dapet layan kurang kena dr mba mba tawar jgn maksa gitu mengangu kenyam customer lg nada bicara kurang humbel terimaksi</t>
+          <t>layan kurang ramah kes maksa order order but think sharing even emg coba pelan mbaa</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6723,16 +6715,16 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>0.0003</v>
+        <v>0.1152</v>
       </c>
       <c r="L80" t="n">
-        <v>0.9997</v>
+        <v>0.8848</v>
       </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="b">
         <v>0</v>
@@ -6773,16 +6765,16 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Suasana ga kaya cafe tapi lebih ke warung, makanan ada yg enak ada yg ga enak. Pesen singkong goreng tapi singkongnya pahit. Pesen Ricebowl Baso enak. Harga worth lah di kelasnya.</t>
+          <t>Punten ya min, habis dapet pelayanan yang kurang mengenakan dr mba mba nya, kalau menawarkan bisa jgn terlalu maksa gitu, mengangu kenyaman sebagai customer, apa lg dengan nada bicara yang kurang humbel, terimaksi????</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>suasana ga kaya cafe warung makan enak ga enak sen singkong goreng singkong pahit sen ricebowl baso enak harga worth kelas</t>
+          <t>punten min habis dapet layan kurang kena dr mba mba tawar jgn maksa gitu mengangu kenyam customer lg nada bicara kurang humbel terimaksi</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -6791,19 +6783,19 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>0.0467</v>
+        <v>0.0003</v>
       </c>
       <c r="L81" t="n">
-        <v>0.9533</v>
+        <v>0.9997</v>
       </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
       <c r="N81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" t="b">
         <v>0</v>
@@ -6841,16 +6833,16 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kedai kopi ini tmpt nya kurang luas ,parkiran juga kurang luas ,rasa kopi nya juga cukupan ,tmpt bersih,pelayanan ramah</t>
+          <t>Suasana ga kaya cafe tapi lebih ke warung, makanan ada yg enak ada yg ga enak. Pesen singkong goreng tapi singkongnya pahit. Pesen Ricebowl Baso enak. Harga worth lah di kelasnya.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>kedai kopi tmpt kurang luas parkir kurang luas kopi cukup tmpt bersih layan ramah</t>
+          <t>suasana ga kaya cafe warung makan enak ga enak sen singkong goreng singkong pahit sen ricebowl baso enak harga worth kelas</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6859,19 +6851,19 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>0.0445</v>
+        <v>0.0467</v>
       </c>
       <c r="L82" t="n">
-        <v>0.9555</v>
+        <v>0.9533</v>
       </c>
       <c r="M82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
       </c>
       <c r="O82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P82" t="b">
         <v>0</v>
@@ -6909,28 +6901,28 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Makanan enaak, pelayanannya oke, ramah dan sangat detail menjelaskan menu²nya.</t>
+          <t>Kedai kopi ini tmpt nya kurang luas ,parkiran juga kurang luas ,rasa kopi nya juga cukupan ,tmpt bersih,pelayanan ramah</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>makan enaak layan oke ramah detail menu nya</t>
+          <t>kedai kopi tmpt kurang luas parkir kurang luas kopi cukup tmpt bersih layan ramah</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>0.9494</v>
+        <v>0.0445</v>
       </c>
       <c r="L83" t="n">
-        <v>0.0506</v>
+        <v>0.9555</v>
       </c>
       <c r="M83" t="b">
         <v>1</v>
@@ -6977,16 +6969,16 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Makanan dan minumannya enak, ada menu sehat buat yg lagi diet. Tempat cocok untuk me time dan nugas, banyak colokan, ada ruangan ber ac dan non ac, pelayanan ramah. Saya datang pas lagi hujan dikasih voucher promo 20%</t>
+          <t>Makanan enaak, pelayanannya oke, ramah dan sangat detail menjelaskan menu²nya.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>makan minum enak menu sehat diet cocok me time nugas colok ruang ber ac non ac layan ramah pas hujan kasih voucher promo</t>
+          <t>makan enaak layan oke ramah detail menu nya</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -6995,22 +6987,22 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>0.6797</v>
+        <v>0.9494</v>
       </c>
       <c r="L84" t="n">
-        <v>0.3203</v>
+        <v>0.0506</v>
       </c>
       <c r="M84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" t="b">
         <v>0</v>
       </c>
       <c r="O84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -7045,16 +7037,16 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tempatnya nyaman dengan suasananya ala vintage, harga makanan dan minumannya worth it untuk kantong mahasiswa dan pekerja.</t>
+          <t>Makanan dan minumannya enak, ada menu sehat buat yg lagi diet. Tempat cocok untuk me time dan nugas, banyak colokan, ada ruangan ber ac dan non ac, pelayanan ramah. Saya datang pas lagi hujan dikasih voucher promo 20%</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>tempat nyaman suasana ala vintage harga makan minum worth it kantong mahasiswa kerja</t>
+          <t>makan minum enak menu sehat diet cocok me time nugas colok ruang ber ac non ac layan ramah pas hujan kasih voucher promo</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7063,22 +7055,22 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>0.9502</v>
+        <v>0.6797</v>
       </c>
       <c r="L85" t="n">
-        <v>0.0498</v>
+        <v>0.3203</v>
       </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
       <c r="N85" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="b">
         <v>1</v>
       </c>
       <c r="P85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -7113,28 +7105,28 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Makanan, kopi, ambience enak bangett tapi sayang kurang customer loyalty nya. Buat tempat duduk kita masih diarahkan dan diatur seperti "Untuk 2 orang bolehnya yang ini ya kak" Dan itu bikin jadi gak nyaman si... pernah sekali memergoki cust memilih keluar dan pindah krn gak diperbolehkan duduk di kursi yg diinginkan. Seharusnya customer yg dateng pertama/duluan bebas memilih tempat.. Thanks</t>
+          <t>Tempatnya nyaman dengan suasananya ala vintage, harga makanan dan minumannya worth it untuk kantong mahasiswa dan pekerja.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>makan kopi ambience enak bangett sayang kurang customer loyalty duduk arah atur orang boleh kak bikin gak nyaman si pergok cust pilih pindah gak boleh duduk kursi customer dateng duluan bebas pilih thanks</t>
+          <t>tempat nyaman suasana ala vintage harga makan minum worth it kantong mahasiswa kerja</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>0.1311</v>
+        <v>0.9502</v>
       </c>
       <c r="L86" t="n">
-        <v>0.8689</v>
+        <v>0.0498</v>
       </c>
       <c r="M86" t="b">
         <v>0</v>
@@ -7143,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="O86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="b">
         <v>0</v>
@@ -7181,34 +7173,34 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Okelah.. singkongnya ok banget... Kopi Wamena nya jossssnya pooolll... tempe Mendoaannya garing garing...</t>
+          <t>Makanan, kopi, ambience enak bangett tapi sayang kurang customer loyalty nya. Buat tempat duduk kita masih diarahkan dan diatur seperti "Untuk 2 orang bolehnya yang ini ya kak" Dan itu bikin jadi gak nyaman si... pernah sekali memergoki cust memilih keluar dan pindah krn gak diperbolehkan duduk di kursi yg diinginkan. Seharusnya customer yg dateng pertama/duluan bebas memilih tempat.. Thanks</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>oke singkong ok kopi wamena jossssnya pooolll tempe doa garing garing</t>
+          <t>makan kopi ambience enak bangett sayang kurang customer loyalty duduk arah atur orang boleh kak bikin gak nyaman si pergok cust pilih pindah gak boleh duduk kursi customer dateng duluan bebas pilih thanks</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>0.9695</v>
+        <v>0.1311</v>
       </c>
       <c r="L87" t="n">
-        <v>0.0305</v>
+        <v>0.8689</v>
       </c>
       <c r="M87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="b">
         <v>0</v>
@@ -7220,27 +7212,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>R008</t>
+          <t>R007</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Batik Hadipriyanto</t>
+          <t>Praketa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Fashion</t>
+          <t>Kuliner</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Banyumas</t>
+          <t>Purwokerto Utara</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Batik, kain, pakaian, dan suvenir berbahan kain</t>
+          <t>Kopi, minuman espresso based, makanan ringan, dan menu kafe</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7249,31 +7241,31 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Toko batik langganan saat pulkam, koleksi lengkap, showroom luas, ber AC dan bersih, bikin betah lama² browsing batik. Pelayanan sat set, ramah daj helpful.</t>
+          <t>Okelah.. singkongnya ok banget... Kopi Wamena nya jossssnya pooolll... tempe Mendoaannya garing garing...</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>toko batik langgan pulkam koleksi lengkap showroom luas ber ac bersih bikin betah lama browsing batik layan sat set ramah daj helpful</t>
+          <t>oke singkong ok kopi wamena jossssnya pooolll tempe doa garing garing</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>0.9529</v>
+        <v>0.9695</v>
       </c>
       <c r="L88" t="n">
-        <v>0.0471</v>
+        <v>0.0305</v>
       </c>
       <c r="M88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -7282,7 +7274,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7317,16 +7309,16 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Batik khas Banyumas, tersedia banyak pilihan, mulai dari yang mahal dengan model batik hasil lukis tangan, sampai yang murah hasil batik stample. Meskipun toko batik khas Banyumas, namun menjual juga beberapa batik khas dari luar daerah seperti kain lurik (surjan), dll.</t>
+          <t>Toko batik langganan saat pulkam, koleksi lengkap, showroom luas, ber AC dan bersih, bikin betah lama² browsing batik. Pelayanan sat set, ramah daj helpful.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>batik khas banyumas sedia pilih mahal model batik hasil lukis tangan murah hasil batik stample toko batik khas banyumas jual batik khas daerah kain lurik surjan dll</t>
+          <t>toko batik langgan pulkam koleksi lengkap showroom luas ber ac bersih bikin betah lama browsing batik layan sat set ramah daj helpful</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7335,10 +7327,10 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>0.6672</v>
+        <v>0.9529</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3328</v>
+        <v>0.0471</v>
       </c>
       <c r="M89" t="b">
         <v>0</v>
@@ -7347,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="O89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
@@ -7385,16 +7377,16 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Pilihan motif batik yg sangat variatif, harga yg terjangkau bahkan dengan layanan yg ramah parkir yg mudah baik untuk roda 2 atau empat.</t>
+          <t>Batik khas Banyumas, tersedia banyak pilihan, mulai dari yang mahal dengan model batik hasil lukis tangan, sampai yang murah hasil batik stample. Meskipun toko batik khas Banyumas, namun menjual juga beberapa batik khas dari luar daerah seperti kain lurik (surjan), dll.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>pilih motif batik variatif harga jangkau layan ramah parkir mudah roda</t>
+          <t>batik khas banyumas sedia pilih mahal model batik hasil lukis tangan murah hasil batik stample toko batik khas banyumas jual batik khas daerah kain lurik surjan dll</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7403,10 +7395,10 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>0.9926</v>
+        <v>0.6672</v>
       </c>
       <c r="L90" t="n">
-        <v>0.0074</v>
+        <v>0.3328</v>
       </c>
       <c r="M90" t="b">
         <v>0</v>
@@ -7418,7 +7410,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -7453,16 +7445,16 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Motif, corak, kain dan modelnya cakep2 semua.. bisa liat proses pembuatannya langsung.. harganya jg sesuai.. Batik Hadipriyanto, Banyumas banget</t>
+          <t>Pilihan motif batik yg sangat variatif, harga yg terjangkau bahkan dengan layanan yg ramah parkir yg mudah baik untuk roda 2 atau empat.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>motif corak kain model cakep liat proses buat langsung harga sesuai batik hadipriyanto banyumas</t>
+          <t>pilih motif batik variatif harga jangkau layan ramah parkir mudah roda</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7471,13 +7463,13 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>0.9748</v>
+        <v>0.9926</v>
       </c>
       <c r="L91" t="n">
-        <v>0.0252</v>
+        <v>0.0074</v>
       </c>
       <c r="M91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -7521,28 +7513,28 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Butik Batik asli Banyumas. Tersedia kain dan busana pria dan wanita jadi. Sayangnya koleksi kurang lengkap. Untuk batik tulis selembar kain seharga ratusan hingga jutaan rupiah.</t>
+          <t>Motif, corak, kain dan modelnya cakep2 semua.. bisa liat proses pembuatannya langsung.. harganya jg sesuai.. Batik Hadipriyanto, Banyumas banget</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>butik batik asli banyumas sedia kain busana pria wanita sayang koleksi kurang lengkap batik tulis lembar kain harga ratus juta rupiah</t>
+          <t>motif corak kain model cakep liat proses buat langsung harga sesuai batik hadipriyanto banyumas</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>0.3274</v>
+        <v>0.9748</v>
       </c>
       <c r="L92" t="n">
-        <v>0.6726</v>
+        <v>0.0252</v>
       </c>
       <c r="M92" t="b">
         <v>1</v>
@@ -7589,16 +7581,16 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bagus nyaman banyak pilihan motif batiknya</t>
+          <t>Butik Batik asli Banyumas. Tersedia kain dan busana pria dan wanita jadi. Sayangnya koleksi kurang lengkap. Untuk batik tulis selembar kain seharga ratusan hingga jutaan rupiah.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>bagus nyaman pilih motif batik</t>
+          <t>butik batik asli banyumas sedia kain busana pria wanita sayang koleksi kurang lengkap batik tulis lembar kain harga ratus juta rupiah</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7607,19 +7599,19 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>0.9973</v>
+        <v>0.3274</v>
       </c>
       <c r="L93" t="n">
-        <v>0.0027</v>
+        <v>0.6726</v>
       </c>
       <c r="M93" t="b">
         <v>1</v>
       </c>
       <c r="N93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P93" t="b">
         <v>0</v>
@@ -7657,37 +7649,37 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Batiknya banyak pilihan. Pemesanan bisa juga melalui WA untuk mengecek ketersediaannya. Pembayaran juga dapat dilakukan secara non tunai.</t>
+          <t>Bagus nyaman banyak pilihan motif batiknya</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>batik pilih mesan wa ecek sedia bayar non tunai</t>
+          <t>bagus nyaman pilih motif batik</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>0.3096</v>
+        <v>0.9973</v>
       </c>
       <c r="L94" t="n">
-        <v>0.6904</v>
+        <v>0.0027</v>
       </c>
       <c r="M94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P94" t="b">
         <v>0</v>
@@ -7725,16 +7717,16 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Produk batiknya lengkap dan harga terjangkau</t>
+          <t>Batiknya banyak pilihan. Pemesanan bisa juga melalui WA untuk mengecek ketersediaannya. Pembayaran juga dapat dilakukan secara non tunai.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>produk batik lengkap harga jangkau</t>
+          <t>batik pilih mesan wa ecek sedia bayar non tunai</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -7743,13 +7735,13 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>0.9961</v>
+        <v>0.3096</v>
       </c>
       <c r="L95" t="n">
-        <v>0.0039</v>
+        <v>0.6904</v>
       </c>
       <c r="M95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N95" t="b">
         <v>0</v>
@@ -7793,16 +7785,16 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Keren dan berkualitas</t>
+          <t>Produk batiknya lengkap dan harga terjangkau</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>keren kualitas</t>
+          <t>produk batik lengkap harga jangkau</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -7811,10 +7803,10 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>0.9996</v>
+        <v>0.9961</v>
       </c>
       <c r="L96" t="n">
-        <v>0.0004</v>
+        <v>0.0039</v>
       </c>
       <c r="M96" t="b">
         <v>1</v>
@@ -7823,7 +7815,7 @@
         <v>0</v>
       </c>
       <c r="O96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" t="b">
         <v>0</v>
@@ -7861,39 +7853,107 @@
         </is>
       </c>
       <c r="G97" t="n">
+        <v>9</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Keren dan berkualitas</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>keren kualitas</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="M97" t="b">
+        <v>1</v>
+      </c>
+      <c r="N97" t="b">
+        <v>0</v>
+      </c>
+      <c r="O97" t="b">
+        <v>0</v>
+      </c>
+      <c r="P97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>R008</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Batik Hadipriyanto</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Banyumas</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Batik, kain, pakaian, dan suvenir berbahan kain</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Google Maps (manual)</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
         <v>10</v>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Tempat yang bagus untuk membeli batik, tetapi ada masalah dengan AC di toko tersebut.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>bagus beli batik ac toko</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="K97" t="n">
+      <c r="K98" t="n">
         <v>0.9157</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L98" t="n">
         <v>0.0843</v>
       </c>
-      <c r="M97" t="b">
-        <v>1</v>
-      </c>
-      <c r="N97" t="b">
-        <v>0</v>
-      </c>
-      <c r="O97" t="b">
-        <v>0</v>
-      </c>
-      <c r="P97" t="b">
+      <c r="M98" t="b">
+        <v>1</v>
+      </c>
+      <c r="N98" t="b">
+        <v>0</v>
+      </c>
+      <c r="O98" t="b">
+        <v>0</v>
+      </c>
+      <c r="P98" t="b">
         <v>0</v>
       </c>
     </row>
